--- a/data/trending_integrated_20261027_14.xlsx
+++ b/data/trending_integrated_20261027_14.xlsx
@@ -578,13 +578,13 @@
         <v>-0.41</v>
       </c>
       <c r="E2" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H2" t="n">
         <v>0.09</v>
@@ -610,7 +610,7 @@
         <v>0.5</v>
       </c>
       <c r="O2" t="n">
-        <v>41968118380</v>
+        <v>41972376650</v>
       </c>
       <c r="P2" t="n">
         <v>28800</v>
@@ -676,7 +676,7 @@
         <v>66</v>
       </c>
       <c r="G3" t="n">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="H3" t="n">
         <v>4.13</v>
@@ -702,7 +702,7 @@
         <v>4.28</v>
       </c>
       <c r="O3" t="n">
-        <v>18739919385</v>
+        <v>18742363255</v>
       </c>
       <c r="P3" t="n">
         <v>28600</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9090</v>
+        <v>9040</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+28.03%</t>
+          <t>'+27.32%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F4" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G4" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H4" t="n">
         <v>2.12</v>
@@ -794,7 +794,7 @@
         <v>2.05</v>
       </c>
       <c r="O4" t="n">
-        <v>44153676060</v>
+        <v>44538191645</v>
       </c>
       <c r="P4" t="n">
         <v>29750</v>
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>앤로보틱스</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2180</v>
+        <v>20450</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.13%</t>
+          <t>'+7.35%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.11</v>
+        <v>0.12</v>
       </c>
       <c r="E5" t="n">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="F5" t="n">
         <v>52</v>
       </c>
       <c r="G5" t="n">
-        <v>215</v>
+        <v>160</v>
       </c>
       <c r="H5" t="n">
-        <v>4.89</v>
+        <v>0.3</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,38 +871,38 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2035</v>
+        <v>19050</v>
       </c>
       <c r="K5" t="n">
-        <v>2035</v>
+        <v>19450</v>
       </c>
       <c r="L5" t="n">
-        <v>2300</v>
+        <v>22450</v>
       </c>
       <c r="M5" t="n">
-        <v>1953</v>
+        <v>18430</v>
       </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>0.18</v>
       </c>
       <c r="O5" t="n">
-        <v>49385058829</v>
+        <v>69826661815</v>
       </c>
       <c r="P5" t="n">
-        <v>4980</v>
+        <v>62100</v>
       </c>
       <c r="Q5" t="n">
-        <v>749</v>
+        <v>14600</v>
       </c>
       <c r="R5" t="n">
-        <v>-41000</v>
+        <v>24000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>로봇 관련주로서 스마트 팩토리 및 자동화 테마 언급. 흑자 전환 기대감 속 변동성 장세.</t>
+          <t>로봇 기업으로 빅웨이브 및 흑자 기업임을 언급. 단기 변동성 및 기술적 분석 기반 상승 여력 논의.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['로봇', '스마트 팩토리', '변동성']</t>
+          <t>['로봇', '흑자기업', '기술적 분석']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,222 +924,222 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>468670</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20300</v>
+        <v>1361000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.56%</t>
+          <t>'+6.75%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.12</v>
+        <v>-0.03</v>
       </c>
       <c r="E6" t="n">
-        <v>90</v>
+        <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>54</v>
+        <v>447</v>
       </c>
       <c r="G6" t="n">
-        <v>162</v>
+        <v>1697</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3</v>
+        <v>48.66</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>19050</v>
+        <v>1275000</v>
       </c>
       <c r="K6" t="n">
-        <v>19450</v>
+        <v>1346000</v>
       </c>
       <c r="L6" t="n">
-        <v>22450</v>
+        <v>1381000</v>
       </c>
       <c r="M6" t="n">
-        <v>18430</v>
+        <v>1341000</v>
       </c>
       <c r="N6" t="n">
-        <v>0.18</v>
+        <v>48.69</v>
       </c>
       <c r="O6" t="n">
-        <v>69463732990</v>
+        <v>2818895147000</v>
       </c>
       <c r="P6" t="n">
-        <v>62100</v>
+        <v>2987000</v>
       </c>
       <c r="Q6" t="n">
-        <v>14600</v>
+        <v>501000</v>
       </c>
       <c r="R6" t="n">
-        <v>24000</v>
+        <v>53000</v>
       </c>
       <c r="S6" t="n">
-        <v>-1000</v>
+        <v>166000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>로봇 기업으로 빅웨이브 및 흑자 기업임을 언급. 단기 변동성 및 기술적 분석 기반 상승 여력 논의.</t>
+          <t>실적 발표 기대감과 외국인·기관 쌍끌이 매수세 유입 속 단기 랠리 전망. 150만원 돌파 가능성 제기.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['로봇', '흑자기업', '기술적 분석']</t>
+          <t>['실적', '외국인', '기관']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>468670</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1356000</v>
+        <v>2140</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.35%</t>
+          <t>'+5.16%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.03</v>
+        <v>-0.11</v>
       </c>
       <c r="E7" t="n">
-        <v>800</v>
+        <v>111</v>
       </c>
       <c r="F7" t="n">
-        <v>448</v>
+        <v>54</v>
       </c>
       <c r="G7" t="n">
-        <v>1694</v>
+        <v>222</v>
       </c>
       <c r="H7" t="n">
-        <v>48.66</v>
+        <v>4.89</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1275000</v>
+        <v>2035</v>
       </c>
       <c r="K7" t="n">
-        <v>1346000</v>
+        <v>2035</v>
       </c>
       <c r="L7" t="n">
-        <v>1381000</v>
+        <v>2300</v>
       </c>
       <c r="M7" t="n">
-        <v>1341000</v>
+        <v>1953</v>
       </c>
       <c r="N7" t="n">
-        <v>48.69</v>
+        <v>5</v>
       </c>
       <c r="O7" t="n">
-        <v>2752477650500</v>
+        <v>49864516840</v>
       </c>
       <c r="P7" t="n">
-        <v>2987000</v>
+        <v>4980</v>
       </c>
       <c r="Q7" t="n">
-        <v>501000</v>
+        <v>749</v>
       </c>
       <c r="R7" t="n">
-        <v>53000</v>
+        <v>-41000</v>
       </c>
       <c r="S7" t="n">
-        <v>166000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>실적 발표 및 주주환원 기대감 속 외국인, 기관의 쌍끌이 매수세 유입. 단기 변동성 예상.</t>
+          <t>로봇 관련주로서 스마트 팩토리 및 자동화 테마 언급. 흑자 전환 기대감 속 변동성 장세.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['실적 발표', '주주환원', '기관 매수']</t>
+          <t>['로봇', '스마트 팩토리', '변동성']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>138360</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>62400</v>
+        <v>223250</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.35%</t>
+          <t>'+4.81%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>147</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>94</v>
+        <v>441</v>
       </c>
       <c r="G8" t="n">
-        <v>876</v>
+        <v>1341</v>
       </c>
       <c r="H8" t="n">
-        <v>40.44</v>
+        <v>46.1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>59800</v>
+        <v>213000</v>
       </c>
       <c r="K8" t="n">
-        <v>60700</v>
+        <v>222000</v>
       </c>
       <c r="L8" t="n">
-        <v>63900</v>
+        <v>225500</v>
       </c>
       <c r="M8" t="n">
-        <v>60100</v>
+        <v>221000</v>
       </c>
       <c r="N8" t="n">
-        <v>40.39</v>
+        <v>46.11</v>
       </c>
       <c r="O8" t="n">
-        <v>230478646650</v>
+        <v>2125558741000</v>
       </c>
       <c r="P8" t="n">
-        <v>67300</v>
+        <v>374500</v>
       </c>
       <c r="Q8" t="n">
-        <v>23150</v>
+        <v>94500</v>
       </c>
       <c r="R8" t="n">
-        <v>219000</v>
+        <v>1190000</v>
       </c>
       <c r="S8" t="n">
-        <v>3000</v>
+        <v>624000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>중동 관련 호재 및 그룹 내 저평가 인식. MSCI 편입 기대감과 대형 수주 공시 가능성 언급.</t>
+          <t>실적 발표 및 주주환원 기대감 속 공매도 세력의 움직임 감지. 외인 매도세 지속.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['중동', ' MSCI', '수주']</t>
+          <t>['실적', '주주환원', '공매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>222250</v>
+        <v>62400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.34%</t>
+          <t>'+4.35%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>800</v>
+        <v>148</v>
       </c>
       <c r="F9" t="n">
-        <v>439</v>
+        <v>95</v>
       </c>
       <c r="G9" t="n">
-        <v>1326</v>
+        <v>881</v>
       </c>
       <c r="H9" t="n">
-        <v>46.1</v>
+        <v>40.44</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>213000</v>
+        <v>59800</v>
       </c>
       <c r="K9" t="n">
-        <v>222000</v>
+        <v>60700</v>
       </c>
       <c r="L9" t="n">
-        <v>225500</v>
+        <v>63900</v>
       </c>
       <c r="M9" t="n">
-        <v>221000</v>
+        <v>60100</v>
       </c>
       <c r="N9" t="n">
-        <v>46.11</v>
+        <v>40.39</v>
       </c>
       <c r="O9" t="n">
-        <v>2060286184750</v>
+        <v>234379673600</v>
       </c>
       <c r="P9" t="n">
-        <v>374500</v>
+        <v>67300</v>
       </c>
       <c r="Q9" t="n">
-        <v>94500</v>
+        <v>23150</v>
       </c>
       <c r="R9" t="n">
-        <v>1190000</v>
+        <v>219000</v>
       </c>
       <c r="S9" t="n">
-        <v>624000</v>
+        <v>3000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>실적 및 주주환원 발표 기대감 속 공매도 세력의 움직임 감지. 긍정 및 부정 전망 혼재.</t>
+          <t>중동 관련 호재 및 그룹 내 저평가 인식. MSCI 편입 기대감과 대형 수주 공시 가능성 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['실적', '주주환원', '공매도']</t>
+          <t>['중동', ' MSCI', '수주']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13740</v>
+        <v>13810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.69%</t>
+          <t>'+3.21%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F10" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G10" t="n">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="H10" t="n">
         <v>2.82</v>
@@ -1346,7 +1346,7 @@
         <v>2.82</v>
       </c>
       <c r="O10" t="n">
-        <v>58734386005</v>
+        <v>59679865675</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14590</v>
+        <v>14570</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.60%</t>
+          <t>'+2.46%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="F11" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G11" t="n">
-        <v>468</v>
+        <v>516</v>
       </c>
       <c r="H11" t="n">
         <v>10.02</v>
@@ -1438,7 +1438,7 @@
         <v>10.03</v>
       </c>
       <c r="O11" t="n">
-        <v>38338008435</v>
+        <v>38664877225</v>
       </c>
       <c r="P11" t="n">
         <v>40350</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16590</v>
+        <v>16550</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+1.78%</t>
+          <t>'+1.53%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.02</v>
       </c>
       <c r="E12" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G12" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H12" t="n">
         <v>27.96</v>
@@ -1530,7 +1530,7 @@
         <v>27.94</v>
       </c>
       <c r="O12" t="n">
-        <v>41539604725</v>
+        <v>42941371315</v>
       </c>
       <c r="P12" t="n">
         <v>35350</v>
@@ -1575,79 +1575,79 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>26500</v>
+        <v>14720</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'+0.20%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.46</v>
       </c>
       <c r="E13" t="n">
-        <v>86</v>
+        <v>164</v>
       </c>
       <c r="F13" t="n">
-        <v>58</v>
+        <v>98</v>
       </c>
       <c r="G13" t="n">
-        <v>289</v>
+        <v>565</v>
       </c>
       <c r="H13" t="n">
-        <v>12.32</v>
+        <v>7.82</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>26500</v>
+        <v>14690</v>
       </c>
       <c r="K13" t="n">
-        <v>26600</v>
+        <v>14490</v>
       </c>
       <c r="L13" t="n">
-        <v>27200</v>
+        <v>15800</v>
       </c>
       <c r="M13" t="n">
-        <v>25350</v>
+        <v>14260</v>
       </c>
       <c r="N13" t="n">
-        <v>12.39</v>
+        <v>7.36</v>
       </c>
       <c r="O13" t="n">
-        <v>45758785375</v>
+        <v>80332145590</v>
       </c>
       <c r="P13" t="n">
-        <v>59300</v>
+        <v>49800</v>
       </c>
       <c r="Q13" t="n">
-        <v>22000</v>
+        <v>8180</v>
       </c>
       <c r="R13" t="n">
-        <v>-236000</v>
+        <v>50000</v>
       </c>
       <c r="S13" t="n">
-        <v>-68000</v>
+        <v>109000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>3분기 실적 발표에 대한 우려와 함께 주가 하락세 지속. 유증 관련 불만 및 태양광 업황 부진 언급.</t>
+          <t>해외 수출 및 신약 개발 관련 긍정적 전망. AI 신약 개발 활용 및 성장성 확장성 확고. 공매도 숏커버링 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['실적', '주가 하락', '태양광']</t>
+          <t>['AI 신약 개발', '수출', '성장성']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1655,23 +1655,23 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>328130</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14690</v>
+        <v>26500</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1679,67 +1679,67 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.46</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>161</v>
+        <v>90</v>
       </c>
       <c r="F14" t="n">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="G14" t="n">
-        <v>559</v>
+        <v>289</v>
       </c>
       <c r="H14" t="n">
-        <v>7.82</v>
+        <v>12.32</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>14690</v>
+        <v>26500</v>
       </c>
       <c r="K14" t="n">
-        <v>14490</v>
+        <v>26600</v>
       </c>
       <c r="L14" t="n">
-        <v>15800</v>
+        <v>27200</v>
       </c>
       <c r="M14" t="n">
-        <v>14260</v>
+        <v>25350</v>
       </c>
       <c r="N14" t="n">
-        <v>7.36</v>
+        <v>12.39</v>
       </c>
       <c r="O14" t="n">
-        <v>79690840475</v>
+        <v>46409797550</v>
       </c>
       <c r="P14" t="n">
-        <v>49800</v>
+        <v>59300</v>
       </c>
       <c r="Q14" t="n">
-        <v>8180</v>
+        <v>22000</v>
       </c>
       <c r="R14" t="n">
-        <v>50000</v>
+        <v>-236000</v>
       </c>
       <c r="S14" t="n">
-        <v>109000</v>
+        <v>-68000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>해외 수출 및 신약 개발 관련 긍정적 전망. AI 신약 개발 활용 및 성장성 확장성 확고. 공매도 숏커버링 기대.</t>
+          <t>3분기 실적 발표에 대한 우려와 함께 주가 하락세 지속. 유증 관련 불만 및 태양광 업황 부진 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['AI 신약 개발', '수출', '성장성']</t>
+          <t>['실적', '주가 하락', '태양광']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1747,12 +1747,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>009830</t>
         </is>
       </c>
     </row>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>34500</v>
+        <v>35200</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-5.48%</t>
+          <t>'-3.56%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1780,7 +1780,7 @@
         <v>94</v>
       </c>
       <c r="G15" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="H15" t="n">
         <v>8.65</v>
@@ -1806,7 +1806,7 @@
         <v>8.029999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>110445672125</v>
+        <v>113276629775</v>
       </c>
       <c r="P15" t="n">
         <v>126600</v>

--- a/data/trending_integrated_20261027_14.xlsx
+++ b/data/trending_integrated_20261027_14.xlsx
@@ -610,7 +610,7 @@
         <v>0.5</v>
       </c>
       <c r="O2" t="n">
-        <v>41972376650</v>
+        <v>41977917150</v>
       </c>
       <c r="P2" t="n">
         <v>28800</v>
@@ -676,7 +676,7 @@
         <v>66</v>
       </c>
       <c r="G3" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H3" t="n">
         <v>4.13</v>
@@ -702,7 +702,7 @@
         <v>4.28</v>
       </c>
       <c r="O3" t="n">
-        <v>18742363255</v>
+        <v>18743508285</v>
       </c>
       <c r="P3" t="n">
         <v>28600</v>
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9040</v>
+        <v>9050</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+27.32%</t>
+          <t>'+27.46%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -768,7 +768,7 @@
         <v>47</v>
       </c>
       <c r="G4" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H4" t="n">
         <v>2.12</v>
@@ -794,7 +794,7 @@
         <v>2.05</v>
       </c>
       <c r="O4" t="n">
-        <v>44538191645</v>
+        <v>45234727470</v>
       </c>
       <c r="P4" t="n">
         <v>29750</v>
@@ -803,7 +803,7 @@
         <v>6570</v>
       </c>
       <c r="R4" t="n">
-        <v>59000</v>
+        <v>84000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20450</v>
+        <v>20300</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.35%</t>
+          <t>'+6.56%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.12</v>
       </c>
       <c r="E5" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F5" t="n">
         <v>52</v>
       </c>
       <c r="G5" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H5" t="n">
         <v>0.3</v>
@@ -886,7 +886,7 @@
         <v>0.18</v>
       </c>
       <c r="O5" t="n">
-        <v>69826661815</v>
+        <v>70115403665</v>
       </c>
       <c r="P5" t="n">
         <v>62100</v>
@@ -895,7 +895,7 @@
         <v>14600</v>
       </c>
       <c r="R5" t="n">
-        <v>24000</v>
+        <v>32000</v>
       </c>
       <c r="S5" t="n">
         <v>-1000</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1361000</v>
+        <v>1351000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.75%</t>
+          <t>'+5.96%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="G6" t="n">
-        <v>1697</v>
+        <v>1721</v>
       </c>
       <c r="H6" t="n">
         <v>48.66</v>
@@ -978,7 +978,7 @@
         <v>48.69</v>
       </c>
       <c r="O6" t="n">
-        <v>2818895147000</v>
+        <v>2885046174000</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>
@@ -987,14 +987,14 @@
         <v>501000</v>
       </c>
       <c r="R6" t="n">
-        <v>53000</v>
+        <v>28000</v>
       </c>
       <c r="S6" t="n">
-        <v>166000</v>
+        <v>168000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>실적 발표 기대감과 외국인·기관 쌍끌이 매수세 유입 속 단기 랠리 전망. 150만원 돌파 가능성 제기.</t>
+          <t>SK하이닉스, 앤트로픽과의 구매 약정 등 신규 호재 언급과 함께 실적 발표 및 주주환원 기대감 형성. 외국인, 기관 동반 매수세 유입으로 단기 상승 모멘텀 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['실적', '외국인', '기관']</t>
+          <t>['앤트로픽', '실적 발표', '주주환원']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,123 +1023,123 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>앤로보틱스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2140</v>
+        <v>222000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.16%</t>
+          <t>'+4.23%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.11</v>
+        <v>-0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>111</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>54</v>
+        <v>441</v>
       </c>
       <c r="G7" t="n">
-        <v>222</v>
+        <v>1365</v>
       </c>
       <c r="H7" t="n">
-        <v>4.89</v>
+        <v>46.1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>2035</v>
+        <v>213000</v>
       </c>
       <c r="K7" t="n">
-        <v>2035</v>
+        <v>222000</v>
       </c>
       <c r="L7" t="n">
-        <v>2300</v>
+        <v>225500</v>
       </c>
       <c r="M7" t="n">
-        <v>1953</v>
+        <v>221000</v>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>46.11</v>
       </c>
       <c r="O7" t="n">
-        <v>49864516840</v>
+        <v>2178933900500</v>
       </c>
       <c r="P7" t="n">
-        <v>4980</v>
+        <v>374500</v>
       </c>
       <c r="Q7" t="n">
-        <v>749</v>
+        <v>94500</v>
       </c>
       <c r="R7" t="n">
-        <v>-41000</v>
+        <v>1197000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>668000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>로봇 관련주로서 스마트 팩토리 및 자동화 테마 언급. 흑자 전환 기대감 속 변동성 장세.</t>
+          <t>삼성전자, 실적 및 주주환원 발표 예정 속 투자 심리 혼조. 공매도 세력 관련 언급 및 향후 주가 상승 기대와 더불어 외인 매도세, 개인 투자자들의 피로감도 감지됨.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['로봇', '스마트 팩토리', '변동성']</t>
+          <t>['실적 발표', '주주환원', '외인 매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>223250</v>
+        <v>62200</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.81%</t>
+          <t>'+4.01%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>149</v>
       </c>
       <c r="F8" t="n">
-        <v>441</v>
+        <v>96</v>
       </c>
       <c r="G8" t="n">
-        <v>1341</v>
+        <v>914</v>
       </c>
       <c r="H8" t="n">
-        <v>46.1</v>
+        <v>40.44</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>213000</v>
+        <v>59800</v>
       </c>
       <c r="K8" t="n">
-        <v>222000</v>
+        <v>60700</v>
       </c>
       <c r="L8" t="n">
-        <v>225500</v>
+        <v>63900</v>
       </c>
       <c r="M8" t="n">
-        <v>221000</v>
+        <v>60100</v>
       </c>
       <c r="N8" t="n">
-        <v>46.11</v>
+        <v>40.39</v>
       </c>
       <c r="O8" t="n">
-        <v>2125558741000</v>
+        <v>237317388550</v>
       </c>
       <c r="P8" t="n">
-        <v>374500</v>
+        <v>67300</v>
       </c>
       <c r="Q8" t="n">
-        <v>94500</v>
+        <v>23150</v>
       </c>
       <c r="R8" t="n">
-        <v>1190000</v>
+        <v>406000</v>
       </c>
       <c r="S8" t="n">
-        <v>624000</v>
+        <v>-25000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>실적 발표 및 주주환원 기대감 속 공매도 세력의 움직임 감지. 외인 매도세 지속.</t>
+          <t>삼성E&amp;A, 중동 지역 수주 기대감 및 그룹사 투자 모멘텀에 따른 주가 상승 전망. MSCI 편입 기대감과 함께 저평가 매력이 부각되며 긍정적 투심 형성.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['실적', '주주환원', '공매도']</t>
+          <t>['중동 수주', 'MSCI 편입', '저평가']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,86 +1200,86 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>62400</v>
+        <v>2110</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.35%</t>
+          <t>'+3.69%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.05</v>
+        <v>-0.11</v>
       </c>
       <c r="E9" t="n">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="F9" t="n">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="G9" t="n">
-        <v>881</v>
+        <v>228</v>
       </c>
       <c r="H9" t="n">
-        <v>40.44</v>
+        <v>4.89</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>59800</v>
+        <v>2035</v>
       </c>
       <c r="K9" t="n">
-        <v>60700</v>
+        <v>2035</v>
       </c>
       <c r="L9" t="n">
-        <v>63900</v>
+        <v>2300</v>
       </c>
       <c r="M9" t="n">
-        <v>60100</v>
+        <v>1953</v>
       </c>
       <c r="N9" t="n">
-        <v>40.39</v>
+        <v>5</v>
       </c>
       <c r="O9" t="n">
-        <v>234379673600</v>
+        <v>50838483661</v>
       </c>
       <c r="P9" t="n">
-        <v>67300</v>
+        <v>4980</v>
       </c>
       <c r="Q9" t="n">
-        <v>23150</v>
+        <v>749</v>
       </c>
       <c r="R9" t="n">
-        <v>219000</v>
+        <v>-35000</v>
       </c>
       <c r="S9" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>중동 관련 호재 및 그룹 내 저평가 인식. MSCI 편입 기대감과 대형 수주 공시 가능성 언급.</t>
+          <t>로봇 관련주로서 스마트 팩토리 및 자동화 테마 언급. 흑자 전환 기대감 속 변동성 장세.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['중동', ' MSCI', '수주']</t>
+          <t>['로봇', '스마트 팩토리', '변동성']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1287,12 +1287,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>138360</t>
         </is>
       </c>
     </row>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13810</v>
+        <v>13820</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.21%</t>
+          <t>'+3.29%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F10" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G10" t="n">
         <v>332</v>
@@ -1346,7 +1346,7 @@
         <v>2.82</v>
       </c>
       <c r="O10" t="n">
-        <v>59679865675</v>
+        <v>60374696440</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1355,10 +1355,10 @@
         <v>1760</v>
       </c>
       <c r="R10" t="n">
-        <v>-212000</v>
+        <v>-199000</v>
       </c>
       <c r="S10" t="n">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14570</v>
+        <v>14530</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.46%</t>
+          <t>'+2.18%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F11" t="n">
         <v>65</v>
       </c>
       <c r="G11" t="n">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H11" t="n">
         <v>10.02</v>
@@ -1438,7 +1438,7 @@
         <v>10.03</v>
       </c>
       <c r="O11" t="n">
-        <v>38664877225</v>
+        <v>39101227585</v>
       </c>
       <c r="P11" t="n">
         <v>40350</v>
@@ -1447,10 +1447,10 @@
         <v>3320</v>
       </c>
       <c r="R11" t="n">
-        <v>197000</v>
+        <v>176000</v>
       </c>
       <c r="S11" t="n">
-        <v>38000</v>
+        <v>40000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16550</v>
+        <v>16530</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+1.53%</t>
+          <t>'+1.41%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.02</v>
       </c>
       <c r="E12" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F12" t="n">
         <v>51</v>
       </c>
       <c r="G12" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="H12" t="n">
         <v>27.96</v>
@@ -1530,7 +1530,7 @@
         <v>27.94</v>
       </c>
       <c r="O12" t="n">
-        <v>42941371315</v>
+        <v>43789410160</v>
       </c>
       <c r="P12" t="n">
         <v>35350</v>
@@ -1539,10 +1539,10 @@
         <v>16270</v>
       </c>
       <c r="R12" t="n">
-        <v>125000</v>
+        <v>21000</v>
       </c>
       <c r="S12" t="n">
-        <v>-32000</v>
+        <v>-17000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14720</v>
+        <v>14700</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.20%</t>
+          <t>'+0.07%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.46</v>
       </c>
       <c r="E13" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F13" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G13" t="n">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="H13" t="n">
         <v>7.82</v>
@@ -1622,7 +1622,7 @@
         <v>7.36</v>
       </c>
       <c r="O13" t="n">
-        <v>80332145590</v>
+        <v>80766659220</v>
       </c>
       <c r="P13" t="n">
         <v>49800</v>
@@ -1631,10 +1631,10 @@
         <v>8180</v>
       </c>
       <c r="R13" t="n">
-        <v>50000</v>
+        <v>48000</v>
       </c>
       <c r="S13" t="n">
-        <v>109000</v>
+        <v>125000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26500</v>
+        <v>26350</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'-0.57%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F14" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G14" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H14" t="n">
         <v>12.32</v>
@@ -1714,7 +1714,7 @@
         <v>12.39</v>
       </c>
       <c r="O14" t="n">
-        <v>46409797550</v>
+        <v>47040251800</v>
       </c>
       <c r="P14" t="n">
         <v>59300</v>
@@ -1723,10 +1723,10 @@
         <v>22000</v>
       </c>
       <c r="R14" t="n">
-        <v>-236000</v>
+        <v>-282000</v>
       </c>
       <c r="S14" t="n">
-        <v>-68000</v>
+        <v>-84000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>35200</v>
+        <v>35050</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.56%</t>
+          <t>'-3.97%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.62</v>
       </c>
       <c r="E15" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F15" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G15" t="n">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="H15" t="n">
         <v>8.65</v>
@@ -1806,7 +1806,7 @@
         <v>8.029999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>113276629775</v>
+        <v>114832837800</v>
       </c>
       <c r="P15" t="n">
         <v>126600</v>
@@ -1818,11 +1818,11 @@
         <v>-393000</v>
       </c>
       <c r="S15" t="n">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>영업이익 전년비 157% 상승에도 불구하고 주가 하락. 외인 매도세와 프로그램 매매 관측.</t>
+          <t>RF머트리얼즈, 전년 대비 157% 상승한 영업이익에도 불구하고 주가 하락 및 개미 털기 의혹 제기. 루멘텀 급등 등 개별 이슈와 함께 시장 반응은 혼조.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['영업이익', '외인 매도', '프로그램 매매']</t>
+          <t>['영업이익', '주가 하락', '물량 던지기']</t>
         </is>
       </c>
       <c r="X15" t="n">

--- a/data/trending_integrated_20261027_14.xlsx
+++ b/data/trending_integrated_20261027_14.xlsx
@@ -610,7 +610,7 @@
         <v>0.5</v>
       </c>
       <c r="O2" t="n">
-        <v>41977917150</v>
+        <v>41990011270</v>
       </c>
       <c r="P2" t="n">
         <v>28800</v>
@@ -670,13 +670,13 @@
         <v>-0.15</v>
       </c>
       <c r="E3" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F3" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G3" t="n">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="H3" t="n">
         <v>4.13</v>
@@ -702,7 +702,7 @@
         <v>4.28</v>
       </c>
       <c r="O3" t="n">
-        <v>18743508285</v>
+        <v>18748754915</v>
       </c>
       <c r="P3" t="n">
         <v>28600</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9050</v>
+        <v>8940</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+27.46%</t>
+          <t>'+25.92%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G4" t="n">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H4" t="n">
         <v>2.12</v>
@@ -794,7 +794,7 @@
         <v>2.05</v>
       </c>
       <c r="O4" t="n">
-        <v>45234727470</v>
+        <v>46324708120</v>
       </c>
       <c r="P4" t="n">
         <v>29750</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20300</v>
+        <v>20400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.56%</t>
+          <t>'+7.09%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.12</v>
       </c>
       <c r="E5" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F5" t="n">
         <v>52</v>
       </c>
       <c r="G5" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H5" t="n">
         <v>0.3</v>
@@ -886,7 +886,7 @@
         <v>0.18</v>
       </c>
       <c r="O5" t="n">
-        <v>70115403665</v>
+        <v>70430988640</v>
       </c>
       <c r="P5" t="n">
         <v>62100</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1351000</v>
+        <v>1346000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.96%</t>
+          <t>'+5.57%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="G6" t="n">
-        <v>1721</v>
+        <v>1750</v>
       </c>
       <c r="H6" t="n">
         <v>48.66</v>
@@ -978,7 +978,7 @@
         <v>48.69</v>
       </c>
       <c r="O6" t="n">
-        <v>2885046174000</v>
+        <v>2967336562500</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>SK하이닉스, 앤트로픽과의 구매 약정 등 신규 호재 언급과 함께 실적 발표 및 주주환원 기대감 형성. 외국인, 기관 동반 매수세 유입으로 단기 상승 모멘텀 기대.</t>
+          <t>외국인, 기관의 쌍끌이 매수세와 실적 발표 및 주주환원 발표 기대감으로 상승세. 다만, 일부에서는 상승 탄력 둔화 우려도 존재.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['앤트로픽', '실적 발표', '주주환원']</t>
+          <t>['실적발표', '주주환원', '수급']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,83 +1023,83 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>222000</v>
+        <v>2130</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.23%</t>
+          <t>'+4.67%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.01</v>
+        <v>-0.11</v>
       </c>
       <c r="E7" t="n">
-        <v>800</v>
+        <v>121</v>
       </c>
       <c r="F7" t="n">
-        <v>441</v>
+        <v>57</v>
       </c>
       <c r="G7" t="n">
-        <v>1365</v>
+        <v>236</v>
       </c>
       <c r="H7" t="n">
-        <v>46.1</v>
+        <v>4.89</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>213000</v>
+        <v>2035</v>
       </c>
       <c r="K7" t="n">
-        <v>222000</v>
+        <v>2035</v>
       </c>
       <c r="L7" t="n">
-        <v>225500</v>
+        <v>2300</v>
       </c>
       <c r="M7" t="n">
-        <v>221000</v>
+        <v>1953</v>
       </c>
       <c r="N7" t="n">
-        <v>46.11</v>
+        <v>5</v>
       </c>
       <c r="O7" t="n">
-        <v>2178933900500</v>
+        <v>51661936764</v>
       </c>
       <c r="P7" t="n">
-        <v>374500</v>
+        <v>4980</v>
       </c>
       <c r="Q7" t="n">
-        <v>94500</v>
+        <v>749</v>
       </c>
       <c r="R7" t="n">
-        <v>1197000</v>
+        <v>-35000</v>
       </c>
       <c r="S7" t="n">
-        <v>668000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>삼성전자, 실적 및 주주환원 발표 예정 속 투자 심리 혼조. 공매도 세력 관련 언급 및 향후 주가 상승 기대와 더불어 외인 매도세, 개인 투자자들의 피로감도 감지됨.</t>
+          <t>로봇 관련주로 분류되며 2026 로보월드 행사 기대감이 있으나, 변동성이 크고 투자 주의 예고로 인해 상승 기대와 우려가 공존.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['실적 발표', '주주환원', '외인 매도']</t>
+          <t>['로봇', '로보월드', '변동성']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>138360</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>62200</v>
+        <v>221750</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.01%</t>
+          <t>'+4.11%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>149</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>96</v>
+        <v>442</v>
       </c>
       <c r="G8" t="n">
-        <v>914</v>
+        <v>1386</v>
       </c>
       <c r="H8" t="n">
-        <v>40.44</v>
+        <v>46.1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>59800</v>
+        <v>213000</v>
       </c>
       <c r="K8" t="n">
-        <v>60700</v>
+        <v>222000</v>
       </c>
       <c r="L8" t="n">
-        <v>63900</v>
+        <v>225500</v>
       </c>
       <c r="M8" t="n">
-        <v>60100</v>
+        <v>221000</v>
       </c>
       <c r="N8" t="n">
-        <v>40.39</v>
+        <v>46.11</v>
       </c>
       <c r="O8" t="n">
-        <v>237317388550</v>
+        <v>2231361662000</v>
       </c>
       <c r="P8" t="n">
-        <v>67300</v>
+        <v>374500</v>
       </c>
       <c r="Q8" t="n">
-        <v>23150</v>
+        <v>94500</v>
       </c>
       <c r="R8" t="n">
-        <v>406000</v>
+        <v>1197000</v>
       </c>
       <c r="S8" t="n">
-        <v>-25000</v>
+        <v>668000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>삼성E&amp;A, 중동 지역 수주 기대감 및 그룹사 투자 모멘텀에 따른 주가 상승 전망. MSCI 편입 기대감과 함께 저평가 매력이 부각되며 긍정적 투심 형성.</t>
+          <t>대통령 골프 논란 속에서 실적 및 주주환원 발표를 앞두고 상승 기대감 존재. 다만, 외인 매도세와 SK하이닉스 ETF 퇴장 뉴스가 부정적 영향.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['중동 수주', 'MSCI 편입', '저평가']</t>
+          <t>['실적', '주주환원', '외인매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,86 +1200,86 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>앤로보틱스</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2110</v>
+        <v>62000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.69%</t>
+          <t>'+3.68%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.11</v>
+        <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>115</v>
+        <v>151</v>
       </c>
       <c r="F9" t="n">
-        <v>56</v>
+        <v>97</v>
       </c>
       <c r="G9" t="n">
-        <v>228</v>
+        <v>924</v>
       </c>
       <c r="H9" t="n">
-        <v>4.89</v>
+        <v>40.44</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>2035</v>
+        <v>59800</v>
       </c>
       <c r="K9" t="n">
-        <v>2035</v>
+        <v>60700</v>
       </c>
       <c r="L9" t="n">
-        <v>2300</v>
+        <v>63900</v>
       </c>
       <c r="M9" t="n">
-        <v>1953</v>
+        <v>60100</v>
       </c>
       <c r="N9" t="n">
-        <v>5</v>
+        <v>40.39</v>
       </c>
       <c r="O9" t="n">
-        <v>50838483661</v>
+        <v>242029740800</v>
       </c>
       <c r="P9" t="n">
-        <v>4980</v>
+        <v>67300</v>
       </c>
       <c r="Q9" t="n">
-        <v>749</v>
+        <v>23150</v>
       </c>
       <c r="R9" t="n">
-        <v>-35000</v>
+        <v>406000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-25000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>로봇 관련주로서 스마트 팩토리 및 자동화 테마 언급. 흑자 전환 기대감 속 변동성 장세.</t>
+          <t>삼성E&amp;A, 중동 지역 수주 기대감 및 그룹사 투자 모멘텀에 따른 주가 상승 전망. MSCI 편입 기대감과 함께 저평가 매력이 부각되며 긍정적 투심 형성.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['로봇', '스마트 팩토리', '변동성']</t>
+          <t>['중동 수주', 'MSCI 편입', '저평가']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1287,12 +1287,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13820</v>
+        <v>13770</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.29%</t>
+          <t>'+2.91%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F10" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G10" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H10" t="n">
         <v>2.82</v>
@@ -1346,7 +1346,7 @@
         <v>2.82</v>
       </c>
       <c r="O10" t="n">
-        <v>60374696440</v>
+        <v>61097017380</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14530</v>
+        <v>14510</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.18%</t>
+          <t>'+2.04%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F11" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G11" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="H11" t="n">
         <v>10.02</v>
@@ -1438,7 +1438,7 @@
         <v>10.03</v>
       </c>
       <c r="O11" t="n">
-        <v>39101227585</v>
+        <v>39574086195</v>
       </c>
       <c r="P11" t="n">
         <v>40350</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>영업이익 223% 폭증에도 불구하고 주가 반등 미미. 실적 발표 후 하락세 우려.</t>
+          <t>223% 영업이익 증가라는 긍정적인 실적 발표가 있었으나, 주가 반등이 미미하고 도배글 신고가 잦아 투자 심리가 혼재.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['영업이익', '실적 발표', '주가 반등']</t>
+          <t>['영업이익', '실적발표', '반등']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16530</v>
+        <v>16470</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+1.41%</t>
+          <t>'+1.04%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.02</v>
       </c>
       <c r="E12" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G12" t="n">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="H12" t="n">
         <v>27.96</v>
@@ -1530,7 +1530,7 @@
         <v>27.94</v>
       </c>
       <c r="O12" t="n">
-        <v>43789410160</v>
+        <v>44814914650</v>
       </c>
       <c r="P12" t="n">
         <v>35350</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14700</v>
+        <v>14480</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.07%</t>
+          <t>'-1.43%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.46</v>
       </c>
       <c r="E13" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F13" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G13" t="n">
-        <v>567</v>
+        <v>584</v>
       </c>
       <c r="H13" t="n">
         <v>7.82</v>
@@ -1622,7 +1622,7 @@
         <v>7.36</v>
       </c>
       <c r="O13" t="n">
-        <v>80766659220</v>
+        <v>81628240730</v>
       </c>
       <c r="P13" t="n">
         <v>49800</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26350</v>
+        <v>26000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.57%</t>
+          <t>'-1.89%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F14" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G14" t="n">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="H14" t="n">
         <v>12.32</v>
@@ -1714,7 +1714,7 @@
         <v>12.39</v>
       </c>
       <c r="O14" t="n">
-        <v>47040251800</v>
+        <v>50261137875</v>
       </c>
       <c r="P14" t="n">
         <v>59300</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>35050</v>
+        <v>34900</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.97%</t>
+          <t>'-4.38%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.62</v>
       </c>
       <c r="E15" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F15" t="n">
         <v>96</v>
       </c>
       <c r="G15" t="n">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="H15" t="n">
         <v>8.65</v>
@@ -1806,7 +1806,7 @@
         <v>8.029999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>114832837800</v>
+        <v>115961095725</v>
       </c>
       <c r="P15" t="n">
         <v>126600</v>

--- a/data/trending_integrated_20261027_14.xlsx
+++ b/data/trending_integrated_20261027_14.xlsx
@@ -610,7 +610,7 @@
         <v>0.5</v>
       </c>
       <c r="O2" t="n">
-        <v>41990011270</v>
+        <v>41994317030</v>
       </c>
       <c r="P2" t="n">
         <v>28800</v>
@@ -702,7 +702,7 @@
         <v>4.28</v>
       </c>
       <c r="O3" t="n">
-        <v>18748754915</v>
+        <v>18748925815</v>
       </c>
       <c r="P3" t="n">
         <v>28600</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8940</v>
+        <v>8930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+25.92%</t>
+          <t>'+25.77%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F4" t="n">
         <v>48</v>
       </c>
       <c r="G4" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H4" t="n">
         <v>2.12</v>
@@ -794,7 +794,7 @@
         <v>2.05</v>
       </c>
       <c r="O4" t="n">
-        <v>46324708120</v>
+        <v>46760766535</v>
       </c>
       <c r="P4" t="n">
         <v>29750</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20400</v>
+        <v>20250</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.09%</t>
+          <t>'+6.30%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.12</v>
       </c>
       <c r="E5" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F5" t="n">
         <v>52</v>
       </c>
       <c r="G5" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H5" t="n">
         <v>0.3</v>
@@ -886,7 +886,7 @@
         <v>0.18</v>
       </c>
       <c r="O5" t="n">
-        <v>70430988640</v>
+        <v>70578496340</v>
       </c>
       <c r="P5" t="n">
         <v>62100</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1346000</v>
+        <v>1342000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.57%</t>
+          <t>'+5.25%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="G6" t="n">
-        <v>1750</v>
+        <v>1733</v>
       </c>
       <c r="H6" t="n">
         <v>48.66</v>
@@ -978,7 +978,7 @@
         <v>48.69</v>
       </c>
       <c r="O6" t="n">
-        <v>2967336562500</v>
+        <v>3027793920500</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2130</v>
+        <v>2120</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.67%</t>
+          <t>'+4.18%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.11</v>
       </c>
       <c r="E7" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F7" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G7" t="n">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="H7" t="n">
         <v>4.89</v>
@@ -1070,7 +1070,7 @@
         <v>5</v>
       </c>
       <c r="O7" t="n">
-        <v>51661936764</v>
+        <v>51920356626</v>
       </c>
       <c r="P7" t="n">
         <v>4980</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>로봇 관련주로 분류되며 2026 로보월드 행사 기대감이 있으나, 변동성이 크고 투자 주의 예고로 인해 상승 기대와 우려가 공존.</t>
+          <t>삼성 관련 언론 보도 언급 및 스마트 팩토리, 로봇 체인 관련 내용 포함. 다만, 투기적 심리가 강하게 나타나 객관적 근거는 부족.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['로봇', '로보월드', '변동성']</t>
+          <t>['스마트 팩토리', '로봇 체인', '언론 보도']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>221750</v>
+        <v>221000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.11%</t>
+          <t>'+3.76%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="G8" t="n">
-        <v>1386</v>
+        <v>1395</v>
       </c>
       <c r="H8" t="n">
         <v>46.1</v>
@@ -1162,7 +1162,7 @@
         <v>46.11</v>
       </c>
       <c r="O8" t="n">
-        <v>2231361662000</v>
+        <v>2277929074750</v>
       </c>
       <c r="P8" t="n">
         <v>374500</v>
@@ -1222,13 +1222,13 @@
         <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F9" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G9" t="n">
-        <v>924</v>
+        <v>932</v>
       </c>
       <c r="H9" t="n">
         <v>40.44</v>
@@ -1254,7 +1254,7 @@
         <v>40.39</v>
       </c>
       <c r="O9" t="n">
-        <v>242029740800</v>
+        <v>245347755100</v>
       </c>
       <c r="P9" t="n">
         <v>67300</v>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13770</v>
+        <v>13750</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.91%</t>
+          <t>'+2.77%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1320,7 +1320,7 @@
         <v>53</v>
       </c>
       <c r="G10" t="n">
-        <v>333</v>
+        <v>366</v>
       </c>
       <c r="H10" t="n">
         <v>2.82</v>
@@ -1346,7 +1346,7 @@
         <v>2.82</v>
       </c>
       <c r="O10" t="n">
-        <v>61097017380</v>
+        <v>61521775020</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14510</v>
+        <v>14460</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.04%</t>
+          <t>'+1.69%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F11" t="n">
         <v>66</v>
       </c>
       <c r="G11" t="n">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="H11" t="n">
         <v>10.02</v>
@@ -1438,7 +1438,7 @@
         <v>10.03</v>
       </c>
       <c r="O11" t="n">
-        <v>39574086195</v>
+        <v>40008474050</v>
       </c>
       <c r="P11" t="n">
         <v>40350</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16470</v>
+        <v>16390</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+1.04%</t>
+          <t>'+0.55%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.02</v>
       </c>
       <c r="E12" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F12" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G12" t="n">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="H12" t="n">
         <v>27.96</v>
@@ -1530,7 +1530,7 @@
         <v>27.94</v>
       </c>
       <c r="O12" t="n">
-        <v>44814914650</v>
+        <v>45842438090</v>
       </c>
       <c r="P12" t="n">
         <v>35350</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14480</v>
+        <v>14450</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.43%</t>
+          <t>'-1.63%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.46</v>
       </c>
       <c r="E13" t="n">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="F13" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G13" t="n">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="H13" t="n">
         <v>7.82</v>
@@ -1622,7 +1622,7 @@
         <v>7.36</v>
       </c>
       <c r="O13" t="n">
-        <v>81628240730</v>
+        <v>82255774705</v>
       </c>
       <c r="P13" t="n">
         <v>49800</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26000</v>
+        <v>25900</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.89%</t>
+          <t>'-2.26%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F14" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G14" t="n">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="H14" t="n">
         <v>12.32</v>
@@ -1714,7 +1714,7 @@
         <v>12.39</v>
       </c>
       <c r="O14" t="n">
-        <v>50261137875</v>
+        <v>52668916575</v>
       </c>
       <c r="P14" t="n">
         <v>59300</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>34900</v>
+        <v>34550</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.38%</t>
+          <t>'-5.34%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.62</v>
       </c>
       <c r="E15" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F15" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G15" t="n">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="H15" t="n">
         <v>8.65</v>
@@ -1806,7 +1806,7 @@
         <v>8.029999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>115961095725</v>
+        <v>116942434775</v>
       </c>
       <c r="P15" t="n">
         <v>126600</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>RF머트리얼즈, 전년 대비 157% 상승한 영업이익에도 불구하고 주가 하락 및 개미 털기 의혹 제기. 루멘텀 급등 등 개별 이슈와 함께 시장 반응은 혼조.</t>
+          <t>전년 대비 큰 폭의 영업이익 상승에도 불구하고, 주가 하락 및 급락에 대한 우려가 존재. 정부의 시장 개입 및 불공정 거래 의혹 제기.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['영업이익', '주가 하락', '물량 던지기']</t>
+          <t>['영업이익', '주가 하락', '불공정 거래']</t>
         </is>
       </c>
       <c r="X15" t="n">

--- a/data/trending_integrated_20261027_14.xlsx
+++ b/data/trending_integrated_20261027_14.xlsx
@@ -584,7 +584,7 @@
         <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H2" t="n">
         <v>0.09</v>
@@ -610,7 +610,7 @@
         <v>0.5</v>
       </c>
       <c r="O2" t="n">
-        <v>41994317030</v>
+        <v>42007281800</v>
       </c>
       <c r="P2" t="n">
         <v>28800</v>
@@ -676,7 +676,7 @@
         <v>65</v>
       </c>
       <c r="G3" t="n">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="H3" t="n">
         <v>4.13</v>
@@ -702,7 +702,7 @@
         <v>4.28</v>
       </c>
       <c r="O3" t="n">
-        <v>18748925815</v>
+        <v>18748942905</v>
       </c>
       <c r="P3" t="n">
         <v>28600</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8930</v>
+        <v>8970</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+25.77%</t>
+          <t>'+26.34%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F4" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G4" t="n">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="H4" t="n">
         <v>2.12</v>
@@ -794,7 +794,7 @@
         <v>2.05</v>
       </c>
       <c r="O4" t="n">
-        <v>46760766535</v>
+        <v>47933438820</v>
       </c>
       <c r="P4" t="n">
         <v>29750</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20250</v>
+        <v>20400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.30%</t>
+          <t>'+7.09%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.12</v>
       </c>
       <c r="E5" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G5" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="H5" t="n">
         <v>0.3</v>
@@ -886,7 +886,7 @@
         <v>0.18</v>
       </c>
       <c r="O5" t="n">
-        <v>70578496340</v>
+        <v>71569590065</v>
       </c>
       <c r="P5" t="n">
         <v>62100</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1342000</v>
+        <v>1345000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.25%</t>
+          <t>'+5.49%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="G6" t="n">
-        <v>1733</v>
+        <v>1664</v>
       </c>
       <c r="H6" t="n">
         <v>48.66</v>
@@ -972,13 +972,13 @@
         <v>1381000</v>
       </c>
       <c r="M6" t="n">
-        <v>1341000</v>
+        <v>1336000</v>
       </c>
       <c r="N6" t="n">
         <v>48.69</v>
       </c>
       <c r="O6" t="n">
-        <v>3027793920500</v>
+        <v>3140666317500</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>외국인, 기관의 쌍끌이 매수세와 실적 발표 및 주주환원 발표 기대감으로 상승세. 다만, 일부에서는 상승 탄력 둔화 우려도 존재.</t>
+          <t>실적 발표 및 주주환원 기대감 속 주가 상승 전망. 외국인 수급 및 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['실적발표', '주주환원', '수급']</t>
+          <t>['실적', '주주환원', '외국인']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2120</v>
+        <v>2125</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.18%</t>
+          <t>'+4.42%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.11</v>
       </c>
       <c r="E7" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F7" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G7" t="n">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="H7" t="n">
         <v>4.89</v>
@@ -1070,7 +1070,7 @@
         <v>5</v>
       </c>
       <c r="O7" t="n">
-        <v>51920356626</v>
+        <v>52343538461</v>
       </c>
       <c r="P7" t="n">
         <v>4980</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>삼성 관련 언론 보도 언급 및 스마트 팩토리, 로봇 체인 관련 내용 포함. 다만, 투기적 심리가 강하게 나타나 객관적 근거는 부족.</t>
+          <t>종가 관리 및 흐름에 대한 긍정적 언급. 삼성전자 연관 및 투자 주의 예고 등.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['스마트 팩토리', '로봇 체인', '언론 보도']</t>
+          <t>['종가관리', '흐름', '투자주의']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>221000</v>
+        <v>62300</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.76%</t>
+          <t>'+4.18%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>157</v>
       </c>
       <c r="F8" t="n">
-        <v>448</v>
+        <v>100</v>
       </c>
       <c r="G8" t="n">
-        <v>1395</v>
+        <v>939</v>
       </c>
       <c r="H8" t="n">
-        <v>46.1</v>
+        <v>40.44</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>213000</v>
+        <v>59800</v>
       </c>
       <c r="K8" t="n">
-        <v>222000</v>
+        <v>60700</v>
       </c>
       <c r="L8" t="n">
-        <v>225500</v>
+        <v>63900</v>
       </c>
       <c r="M8" t="n">
-        <v>221000</v>
+        <v>60100</v>
       </c>
       <c r="N8" t="n">
-        <v>46.11</v>
+        <v>40.39</v>
       </c>
       <c r="O8" t="n">
-        <v>2277929074750</v>
+        <v>252384820200</v>
       </c>
       <c r="P8" t="n">
-        <v>374500</v>
+        <v>67300</v>
       </c>
       <c r="Q8" t="n">
-        <v>94500</v>
+        <v>23150</v>
       </c>
       <c r="R8" t="n">
-        <v>1197000</v>
+        <v>406000</v>
       </c>
       <c r="S8" t="n">
-        <v>668000</v>
+        <v>-25000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>대통령 골프 논란 속에서 실적 및 주주환원 발표를 앞두고 상승 기대감 존재. 다만, 외인 매도세와 SK하이닉스 ETF 퇴장 뉴스가 부정적 영향.</t>
+          <t>삼성E&amp;A, 중동 지역 수주 기대감 및 그룹사 투자 모멘텀에 따른 주가 상승 전망. MSCI 편입 기대감과 함께 저평가 매력이 부각되며 긍정적 투심 형성.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['실적', '주주환원', '외인매도']</t>
+          <t>['중동 수주', 'MSCI 편입', '저평가']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>62000</v>
+        <v>221500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.68%</t>
+          <t>'+3.99%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>155</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>99</v>
+        <v>444</v>
       </c>
       <c r="G9" t="n">
-        <v>932</v>
+        <v>1394</v>
       </c>
       <c r="H9" t="n">
-        <v>40.44</v>
+        <v>46.1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>59800</v>
+        <v>213000</v>
       </c>
       <c r="K9" t="n">
-        <v>60700</v>
+        <v>222000</v>
       </c>
       <c r="L9" t="n">
-        <v>63900</v>
+        <v>225500</v>
       </c>
       <c r="M9" t="n">
-        <v>60100</v>
+        <v>220000</v>
       </c>
       <c r="N9" t="n">
-        <v>40.39</v>
+        <v>46.11</v>
       </c>
       <c r="O9" t="n">
-        <v>245347755100</v>
+        <v>2379715721500</v>
       </c>
       <c r="P9" t="n">
-        <v>67300</v>
+        <v>374500</v>
       </c>
       <c r="Q9" t="n">
-        <v>23150</v>
+        <v>94500</v>
       </c>
       <c r="R9" t="n">
-        <v>406000</v>
+        <v>1197000</v>
       </c>
       <c r="S9" t="n">
-        <v>-25000</v>
+        <v>668000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>삼성E&amp;A, 중동 지역 수주 기대감 및 그룹사 투자 모멘텀에 따른 주가 상승 전망. MSCI 편입 기대감과 함께 저평가 매력이 부각되며 긍정적 투심 형성.</t>
+          <t>실적 및 주주환원 발표 예정 속 기술주 관련 언급. 외인 매매 동향 및 주가 변동성 우려.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['중동 수주', 'MSCI 편입', '저평가']</t>
+          <t>['실적', '주주환원', '외인']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1314,13 +1314,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F10" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G10" t="n">
-        <v>366</v>
+        <v>396</v>
       </c>
       <c r="H10" t="n">
         <v>2.82</v>
@@ -1346,7 +1346,7 @@
         <v>2.82</v>
       </c>
       <c r="O10" t="n">
-        <v>61521775020</v>
+        <v>62231747880</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1406,13 +1406,13 @@
         <v>-0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F11" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G11" t="n">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="H11" t="n">
         <v>10.02</v>
@@ -1432,13 +1432,13 @@
         <v>15150</v>
       </c>
       <c r="M11" t="n">
-        <v>14390</v>
+        <v>14360</v>
       </c>
       <c r="N11" t="n">
         <v>10.03</v>
       </c>
       <c r="O11" t="n">
-        <v>40008474050</v>
+        <v>41278601550</v>
       </c>
       <c r="P11" t="n">
         <v>40350</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16390</v>
+        <v>16410</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.55%</t>
+          <t>'+0.67%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.02</v>
       </c>
       <c r="E12" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F12" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G12" t="n">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="H12" t="n">
         <v>27.96</v>
@@ -1530,7 +1530,7 @@
         <v>27.94</v>
       </c>
       <c r="O12" t="n">
-        <v>45842438090</v>
+        <v>46923775795</v>
       </c>
       <c r="P12" t="n">
         <v>35350</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14450</v>
+        <v>14690</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.63%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.46</v>
       </c>
       <c r="E13" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F13" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G13" t="n">
-        <v>587</v>
+        <v>598</v>
       </c>
       <c r="H13" t="n">
         <v>7.82</v>
@@ -1622,7 +1622,7 @@
         <v>7.36</v>
       </c>
       <c r="O13" t="n">
-        <v>82255774705</v>
+        <v>83323856790</v>
       </c>
       <c r="P13" t="n">
         <v>49800</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>해외 수출 및 신약 개발 관련 긍정적 전망. AI 신약 개발 활용 및 성장성 확장성 확고. 공매도 숏커버링 기대.</t>
+          <t>해외 수출 및 신약 개발 활용 성공 사례 언급. AI 의료주 대장으로서의 성장성 및 확장성 부각.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['AI 신약 개발', '수출', '성장성']</t>
+          <t>['수출', '신약개발', 'AI의료']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25900</v>
+        <v>26150</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.26%</t>
+          <t>'-1.32%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F14" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G14" t="n">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="H14" t="n">
         <v>12.32</v>
@@ -1714,7 +1714,7 @@
         <v>12.39</v>
       </c>
       <c r="O14" t="n">
-        <v>52668916575</v>
+        <v>54734940700</v>
       </c>
       <c r="P14" t="n">
         <v>59300</v>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>34550</v>
+        <v>34650</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-5.34%</t>
+          <t>'-5.07%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,7 +1777,7 @@
         <v>155</v>
       </c>
       <c r="F15" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G15" t="n">
         <v>270</v>
@@ -1806,7 +1806,7 @@
         <v>8.029999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>116942434775</v>
+        <v>118278312000</v>
       </c>
       <c r="P15" t="n">
         <v>126600</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>전년 대비 큰 폭의 영업이익 상승에도 불구하고, 주가 하락 및 급락에 대한 우려가 존재. 정부의 시장 개입 및 불공정 거래 의혹 제기.</t>
+          <t>실적 호조에도 불구하고 주가 하락 및 외인 매도 관련 부정적 언급. 금감원 관련 민원 제기.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['영업이익', '주가 하락', '불공정 거래']</t>
+          <t>['실적', '외인매도', '주가하락']</t>
         </is>
       </c>
       <c r="X15" t="n">
